--- a/Tablas Proyecto.xlsx
+++ b/Tablas Proyecto.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maximiliano\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maximiliano\Desktop\Tecnicatura Redes y Software\Proyecto UTU 2026 TD4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB649636-124E-4EAD-8DB7-6324BE48AB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFE2E4E-89BF-486C-8FD4-68BB75AAE319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6C19CD7-30EE-4CAC-B98D-B8D0EDE6E5E5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>ROL</t>
   </si>
@@ -57,9 +57,6 @@
     <t>FK</t>
   </si>
   <si>
-    <t>FACTURA_PENDIENTE</t>
-  </si>
-  <si>
     <t>monto</t>
   </si>
   <si>
@@ -76,12 +73,6 @@
   </si>
   <si>
     <t>fecha_hora</t>
-  </si>
-  <si>
-    <t>id_FACTURA_PENDIENTE</t>
-  </si>
-  <si>
-    <t>id_USUARIO</t>
   </si>
   <si>
     <t>OBSERVACION</t>
@@ -108,9 +99,6 @@
 Autoincremental</t>
   </si>
   <si>
-    <t>numero/serie</t>
-  </si>
-  <si>
     <t>DATETIME</t>
   </si>
   <si>
@@ -118,9 +106,6 @@
   </si>
   <si>
     <t>VARCHAR(255)</t>
-  </si>
-  <si>
-    <t>*La contraseña va a ir cifrada</t>
   </si>
   <si>
     <t>VARCHAR(20)
@@ -135,19 +120,49 @@
 NOT NULL</t>
   </si>
   <si>
-    <t>ENUM('Cobrado', 'Pendiente')
-NOT NULL</t>
-  </si>
-  <si>
     <t>VARCHAR(255)
 NOT NULL</t>
   </si>
   <si>
-    <t>* Decimal (7,2) permite facturas de hasta $100.000</t>
-  </si>
-  <si>
     <t>DECIMAL(7,2)
 NOT NULL</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>ENUM('Cobrado', 'Pendiente', 'Anulada')
+NOT NULL</t>
+  </si>
+  <si>
+    <t>numero_serie</t>
+  </si>
+  <si>
+    <t>ROL (id, nombre)</t>
+  </si>
+  <si>
+    <t>OBSERVACION (id, detalle, fecha_hora, id_factura, id_usuario)</t>
+  </si>
+  <si>
+    <t>USUARIO (id, usuario, contrasenia, activo, id_rol)</t>
+  </si>
+  <si>
+    <t>MR</t>
+  </si>
+  <si>
+    <t>id_usuario_registro</t>
+  </si>
+  <si>
+    <t>id_usuario_asignado</t>
+  </si>
+  <si>
+    <t>FACTURA (id, numero_serie, monto, fecha_registro, fecha_cobro, estado, id_usuario_registro, id_usuario_asignado)</t>
+  </si>
+  <si>
+    <t>id_factura</t>
+  </si>
+  <si>
+    <t>id_usuario</t>
   </si>
 </sst>
 </file>
@@ -263,43 +278,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -620,227 +641,318 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFAD9C0-1A89-42D7-BA5C-6CFB83A4605D}">
-  <dimension ref="B2:P11"/>
+  <dimension ref="B2:P17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="3"/>
-    <col min="3" max="3" width="3.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="3"/>
-    <col min="7" max="7" width="3.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="4" style="3" customWidth="1"/>
-    <col min="12" max="12" width="27.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.5703125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="25.140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="3.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.7109375" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="1"/>
+    <col min="3" max="3" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4" style="1" customWidth="1"/>
+    <col min="12" max="12" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="2"/>
-      <c r="F2" s="1" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="11"/>
+      <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="2"/>
-      <c r="J2" s="1" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="11"/>
+      <c r="J2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="11"/>
+      <c r="N2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="10"/>
+      <c r="P2" s="11"/>
+    </row>
+    <row r="3" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="2"/>
-      <c r="N2" s="1" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="J6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="F7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="9" t="s">
+      <c r="J7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="J8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="9" t="s">
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+    </row>
+    <row r="13" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="14" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+    </row>
+    <row r="15" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+    </row>
+    <row r="16" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="F7" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="J8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="F9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="J11" s="12" t="s">
-        <v>36</v>
-      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="10">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Tablas Proyecto.xlsx
+++ b/Tablas Proyecto.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maximiliano\Desktop\Tecnicatura Redes y Software\Proyecto UTU 2026 TD4\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFE2E4E-89BF-486C-8FD4-68BB75AAE319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6C19CD7-30EE-4CAC-B98D-B8D0EDE6E5E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
   <si>
     <t>ROL</t>
   </si>
@@ -163,12 +157,78 @@
   </si>
   <si>
     <t>id_usuario</t>
+  </si>
+  <si>
+    <t>int(10)</t>
+  </si>
+  <si>
+    <t>forma_pago</t>
+  </si>
+  <si>
+    <t>liquidado</t>
+  </si>
+  <si>
+    <t>id_repartidor</t>
+  </si>
+  <si>
+    <t>smallint(5)</t>
+  </si>
+  <si>
+    <t>decimal(8,2)</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>tinyint(1)</t>
+  </si>
+  <si>
+    <t>PAGO</t>
+  </si>
+  <si>
+    <t>enum('Efectivo', 'Transferencia', 'Debito', 'Credito','Cheque')</t>
+  </si>
+  <si>
+    <t>accion</t>
+  </si>
+  <si>
+    <t>varchar(30)</t>
+  </si>
+  <si>
+    <t>entidad</t>
+  </si>
+  <si>
+    <t>id_entidad</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>varchar(255)</t>
+  </si>
+  <si>
+    <t>valor_anterior</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>valor_nuevo</t>
+  </si>
+  <si>
+    <t>AUDITORIA</t>
+  </si>
+  <si>
+    <t>PAGO (id, id_factura, id_repartido, monto, forma_pago, fecha_hora, liquidado)</t>
+  </si>
+  <si>
+    <t>AUDITORIA (id, id_usuario, accion, entidad, id_entidad, descripcion, valor_anterior, valor_nuevo, fecha_hora)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -194,7 +254,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,6 +270,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -278,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -301,6 +367,45 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -312,15 +417,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -387,7 +483,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -439,7 +535,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -633,27 +729,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFAD9C0-1A89-42D7-BA5C-6CFB83A4605D}">
-  <dimension ref="B2:P17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="B2:P43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="13.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="4" style="1" customWidth="1"/>
     <col min="12" max="12" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.5703125" style="1" customWidth="1"/>
@@ -664,35 +761,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
-      <c r="F2" s="9" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
+      <c r="F2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
-      <c r="J2" s="9" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+      <c r="J2" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="11"/>
-      <c r="N2" s="9" t="s">
+      <c r="K2" s="23"/>
+      <c r="L2" s="24"/>
+      <c r="N2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="11"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="24"/>
     </row>
     <row r="3" spans="2:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -838,6 +935,11 @@
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
       <c r="J9" s="2" t="s">
         <v>39</v>
       </c>
@@ -847,114 +949,306 @@
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="J10" s="7" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="8" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="12" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-    </row>
-    <row r="13" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="14" t="s">
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="20"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="17"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-    </row>
-    <row r="15" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="17"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-    </row>
-    <row r="16" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="17"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="17"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
-    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B43:L43"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B41:L41"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B39:L39"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B37:L37"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B13:L13"/>
-    <mergeCell ref="B14:L14"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="11" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>